--- a/results/03_crf_transitions_synthetic.xlsx
+++ b/results/03_crf_transitions_synthetic.xlsx
@@ -557,67 +557,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39.66</v>
+        <v>39.42</v>
       </c>
       <c r="C4" t="n">
-        <v>50.06</v>
+        <v>45.26</v>
       </c>
       <c r="D4" t="n">
-        <v>36.31</v>
+        <v>37.25</v>
       </c>
       <c r="E4" t="n">
-        <v>94.7</v>
+        <v>94.77</v>
       </c>
       <c r="F4" t="n">
-        <v>94.56999999999999</v>
+        <v>94.64</v>
       </c>
       <c r="G4" t="n">
-        <v>95.03</v>
+        <v>95.06</v>
       </c>
       <c r="H4" t="n">
-        <v>95.03</v>
+        <v>95.06</v>
       </c>
       <c r="I4" t="n">
-        <v>39.81</v>
+        <v>38.44</v>
       </c>
       <c r="J4" t="n">
-        <v>44.32</v>
+        <v>42.66</v>
       </c>
       <c r="K4" t="n">
-        <v>39.12</v>
+        <v>39.17</v>
       </c>
       <c r="L4" t="n">
-        <v>95.68000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>95.73999999999999</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>95.86</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>95.86</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>40.59</v>
+        <v>43.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.5</v>
+        <v>44.27</v>
       </c>
       <c r="R4" t="n">
-        <v>42.99</v>
+        <v>46.9</v>
       </c>
       <c r="S4" t="n">
-        <v>96.39</v>
+        <v>96.69</v>
       </c>
       <c r="T4" t="n">
-        <v>96.42</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>96.45999999999999</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>96.45999999999999</v>
+        <v>96.68000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12.22</v>
+        <v>13.54</v>
       </c>
       <c r="D4" t="n">
-        <v>26.83</v>
+        <v>24.53</v>
       </c>
       <c r="E4" t="n">
-        <v>7.91</v>
+        <v>9.35</v>
       </c>
       <c r="F4" t="n">
         <v>139</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.12</v>
+        <v>11.27</v>
       </c>
       <c r="D5" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>1.64</v>
+        <v>6.56</v>
       </c>
       <c r="F5" t="n">
         <v>61</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>13.33</v>
       </c>
       <c r="F6" t="n">
         <v>15</v>
@@ -860,10 +860,18 @@
       <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -876,13 +884,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51.13</v>
+        <v>51.4</v>
       </c>
       <c r="D8" t="n">
-        <v>64.84999999999999</v>
+        <v>64.02</v>
       </c>
       <c r="E8" t="n">
-        <v>42.2</v>
+        <v>42.94</v>
       </c>
       <c r="F8" t="n">
         <v>1749</v>
@@ -919,10 +927,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.54</v>
+        <v>21.21</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="E9" t="n">
         <v>17.5</v>
@@ -1024,22 +1032,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>52.75</v>
+        <v>52.17</v>
       </c>
       <c r="D12" t="n">
-        <v>65.47</v>
+        <v>64.75</v>
       </c>
       <c r="E12" t="n">
-        <v>44.17</v>
+        <v>43.69</v>
       </c>
       <c r="F12" t="n">
         <v>206</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
+        <v>50.63</v>
       </c>
       <c r="H12" t="n">
-        <v>83.33</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>35.71</v>
@@ -1067,10 +1075,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>56.72</v>
+        <v>54.29</v>
       </c>
       <c r="D13" t="n">
-        <v>54.29</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
         <v>59.38</v>
@@ -1079,10 +1087,10 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="H13" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="I13" t="n">
         <v>50</v>
@@ -1110,34 +1118,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>48.05</v>
+        <v>49.54</v>
       </c>
       <c r="D14" t="n">
-        <v>56.41</v>
+        <v>56.64</v>
       </c>
       <c r="E14" t="n">
-        <v>41.85</v>
+        <v>44.02</v>
       </c>
       <c r="F14" t="n">
         <v>368</v>
       </c>
       <c r="G14" t="n">
-        <v>62.72</v>
+        <v>54.55</v>
       </c>
       <c r="H14" t="n">
-        <v>56.99</v>
+        <v>44.26</v>
       </c>
       <c r="I14" t="n">
-        <v>69.73999999999999</v>
+        <v>71.05</v>
       </c>
       <c r="J14" t="n">
         <v>76</v>
       </c>
       <c r="K14" t="n">
-        <v>22.22</v>
+        <v>16</v>
       </c>
       <c r="L14" t="n">
-        <v>13.33</v>
+        <v>9.09</v>
       </c>
       <c r="M14" t="n">
         <v>66.67</v>
@@ -1153,13 +1161,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>10</v>
@@ -1188,37 +1196,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>89.61</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>88.84</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>90.39</v>
+        <v>90.66</v>
       </c>
       <c r="F16" t="n">
         <v>12166</v>
       </c>
       <c r="G16" t="n">
-        <v>90.40000000000001</v>
+        <v>90.44</v>
       </c>
       <c r="H16" t="n">
-        <v>91.64</v>
+        <v>91.55</v>
       </c>
       <c r="I16" t="n">
-        <v>89.19</v>
+        <v>89.36</v>
       </c>
       <c r="J16" t="n">
         <v>1758</v>
       </c>
       <c r="K16" t="n">
-        <v>88.63</v>
+        <v>89.81</v>
       </c>
       <c r="L16" t="n">
-        <v>88.63</v>
+        <v>89.13</v>
       </c>
       <c r="M16" t="n">
-        <v>88.63</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>906</v>
@@ -1231,22 +1239,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31.17</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>55.56</v>
       </c>
       <c r="E17" t="n">
-        <v>19.35</v>
+        <v>16.13</v>
       </c>
       <c r="F17" t="n">
         <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="H17" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="I17" t="n">
         <v>25</v>
@@ -1266,22 +1274,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57.25</v>
+        <v>62.88</v>
       </c>
       <c r="D18" t="n">
-        <v>62.02</v>
+        <v>67.56</v>
       </c>
       <c r="E18" t="n">
-        <v>53.16</v>
+        <v>58.8</v>
       </c>
       <c r="F18" t="n">
         <v>301</v>
       </c>
       <c r="G18" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I18" t="n">
         <v>37.5</v>
@@ -1290,13 +1298,13 @@
         <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L18" t="n">
-        <v>66.67</v>
+        <v>33.33</v>
       </c>
       <c r="M18" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
@@ -1309,22 +1317,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>49.66</v>
+        <v>51.1</v>
       </c>
       <c r="D19" t="n">
-        <v>59.79</v>
+        <v>59.91</v>
       </c>
       <c r="E19" t="n">
-        <v>42.46</v>
+        <v>44.56</v>
       </c>
       <c r="F19" t="n">
         <v>1194</v>
       </c>
       <c r="G19" t="n">
-        <v>71.75</v>
+        <v>71.52</v>
       </c>
       <c r="H19" t="n">
-        <v>72.44</v>
+        <v>71.97</v>
       </c>
       <c r="I19" t="n">
         <v>71.06999999999999</v>
@@ -1333,13 +1341,13 @@
         <v>159</v>
       </c>
       <c r="K19" t="n">
-        <v>52.1</v>
+        <v>58.54</v>
       </c>
       <c r="L19" t="n">
-        <v>72.09</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>40.79</v>
+        <v>47.37</v>
       </c>
       <c r="N19" t="n">
         <v>76</v>
@@ -1352,13 +1360,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15.38</v>
+        <v>25.64</v>
       </c>
       <c r="D20" t="n">
-        <v>21.43</v>
+        <v>35.71</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
         <v>25</v>
@@ -1375,18 +1383,10 @@
       <c r="J20" t="n">
         <v>4</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -1395,37 +1395,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>92.56999999999999</v>
+        <v>92.77</v>
       </c>
       <c r="D21" t="n">
-        <v>90.31</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>94.94</v>
+        <v>94.91</v>
       </c>
       <c r="F21" t="n">
         <v>7668</v>
       </c>
       <c r="G21" t="n">
-        <v>95.04000000000001</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>93.7</v>
+        <v>93.86</v>
       </c>
       <c r="I21" t="n">
-        <v>96.42</v>
+        <v>94.56</v>
       </c>
       <c r="J21" t="n">
         <v>1342</v>
       </c>
       <c r="K21" t="n">
-        <v>96.88</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>96.8</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>96.95999999999999</v>
+        <v>95.78</v>
       </c>
       <c r="N21" t="n">
         <v>592</v>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42.86</v>
+        <v>47.44</v>
       </c>
       <c r="D22" t="n">
-        <v>50.53</v>
+        <v>59.3</v>
       </c>
       <c r="E22" t="n">
-        <v>37.21</v>
+        <v>39.53</v>
       </c>
       <c r="F22" t="n">
         <v>129</v>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.48</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>68.52</v>
+        <v>72.67</v>
       </c>
       <c r="E23" t="n">
-        <v>59.13</v>
+        <v>60.1</v>
       </c>
       <c r="F23" t="n">
         <v>416</v>
@@ -1500,13 +1500,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50.82</v>
+        <v>49.64</v>
       </c>
       <c r="D24" t="n">
-        <v>51.24</v>
+        <v>50.31</v>
       </c>
       <c r="E24" t="n">
-        <v>50.41</v>
+        <v>48.98</v>
       </c>
       <c r="F24" t="n">
         <v>490</v>
@@ -1515,22 +1515,22 @@
         <v>40</v>
       </c>
       <c r="H24" t="n">
-        <v>39.02</v>
+        <v>41.67</v>
       </c>
       <c r="I24" t="n">
-        <v>41.03</v>
+        <v>38.46</v>
       </c>
       <c r="J24" t="n">
         <v>39</v>
       </c>
       <c r="K24" t="n">
-        <v>48.89</v>
+        <v>60.47</v>
       </c>
       <c r="L24" t="n">
-        <v>47.83</v>
+        <v>61.9</v>
       </c>
       <c r="M24" t="n">
-        <v>50</v>
+        <v>59.09</v>
       </c>
       <c r="N24" t="n">
         <v>22</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57.45</v>
+        <v>55.48</v>
       </c>
       <c r="D25" t="n">
-        <v>50.94</v>
+        <v>47.93</v>
       </c>
       <c r="E25" t="n">
         <v>65.84999999999999</v>
@@ -1555,13 +1555,13 @@
         <v>123</v>
       </c>
       <c r="G25" t="n">
-        <v>52.94</v>
+        <v>59.46</v>
       </c>
       <c r="H25" t="n">
-        <v>64.29000000000001</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J25" t="n">
         <v>20</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.95</v>
+        <v>15.75</v>
       </c>
       <c r="D26" t="n">
-        <v>43.48</v>
+        <v>31.25</v>
       </c>
       <c r="E26" t="n">
         <v>10.53</v>
@@ -1590,25 +1590,25 @@
         <v>95</v>
       </c>
       <c r="G26" t="n">
-        <v>13.33</v>
+        <v>12.9</v>
       </c>
       <c r="H26" t="n">
-        <v>8.33</v>
+        <v>7.14</v>
       </c>
       <c r="I26" t="n">
-        <v>33.33</v>
+        <v>66.67</v>
       </c>
       <c r="J26" t="n">
         <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N26" t="n">
         <v>2</v>
@@ -1621,22 +1621,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>61.99</v>
+        <v>60.72</v>
       </c>
       <c r="D27" t="n">
-        <v>59.05</v>
+        <v>58.08</v>
       </c>
       <c r="E27" t="n">
-        <v>65.25</v>
+        <v>63.61</v>
       </c>
       <c r="F27" t="n">
         <v>305</v>
       </c>
       <c r="G27" t="n">
-        <v>73.97</v>
+        <v>76.06</v>
       </c>
       <c r="H27" t="n">
-        <v>67.5</v>
+        <v>71.05</v>
       </c>
       <c r="I27" t="n">
         <v>81.81999999999999</v>
@@ -1645,13 +1645,13 @@
         <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>57.14</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>57.14</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>57.14</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="N27" t="n">
         <v>14</v>
@@ -1664,13 +1664,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>42.52</v>
+        <v>46.97</v>
       </c>
       <c r="D28" t="n">
-        <v>48.65</v>
+        <v>51.24</v>
       </c>
       <c r="E28" t="n">
-        <v>37.76</v>
+        <v>43.36</v>
       </c>
       <c r="F28" t="n">
         <v>143</v>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="D29" t="n">
         <v>28.57</v>
       </c>
-      <c r="D29" t="n">
-        <v>50</v>
-      </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>13.33</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>23.08</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>98.12</v>
+        <v>98.13</v>
       </c>
       <c r="D31" t="n">
-        <v>97.66</v>
+        <v>97.75</v>
       </c>
       <c r="E31" t="n">
-        <v>98.58</v>
+        <v>98.52</v>
       </c>
       <c r="F31" t="n">
         <v>101885</v>
@@ -1800,22 +1800,22 @@
         <v>98.2</v>
       </c>
       <c r="H31" t="n">
-        <v>97.62</v>
+        <v>97.69</v>
       </c>
       <c r="I31" t="n">
-        <v>98.78</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>14471</v>
       </c>
       <c r="K31" t="n">
-        <v>98.42</v>
+        <v>98.58</v>
       </c>
       <c r="L31" t="n">
-        <v>98.23</v>
+        <v>98.53</v>
       </c>
       <c r="M31" t="n">
-        <v>98.61</v>
+        <v>98.62</v>
       </c>
       <c r="N31" t="n">
         <v>6815</v>
